--- a/docs/reports/连通标注_2026-07-04_分表/4_公司.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/4_公司.xlsx
@@ -1456,14 +1456,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K3" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K3" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>无 企查查 API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (API套餐约¥数千–数万/年)</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K4" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="K5" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1630,14 +1630,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K6" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K6" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>无 SEC EDGAR API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -1688,14 +1688,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K7" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K7" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·部分需付费</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>无 OpenCorporates API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:部分付费 (API按credit计费,约£/千次)</t>
         </is>
       </c>
     </row>
@@ -1746,14 +1746,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K8" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K8" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>无 Crunchbase API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (Pro $99/月;API企业版$50k+/年)</t>
         </is>
       </c>
     </row>
@@ -1804,14 +1804,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K9" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K9" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>无 IT桔子 API provider 插件</t>
+          <t>验证:HTTP 412</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K10" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1920,14 +1920,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K11" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K11" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>无 Caplight API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (企业订阅,询价)</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K12" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2036,14 +2036,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K13" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K13" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>无 AKShare API (Python库) provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2094,14 +2094,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K14" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K14" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>无 Wind API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (约¥39,800/年/账号)</t>
         </is>
       </c>
     </row>
@@ -2152,14 +2152,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K15" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K15" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>无 富途 OpenAPI provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2210,14 +2210,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K16" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K16" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>无 Yahoo Finance API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="K17" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="K18" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2384,14 +2384,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K19" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K19" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>无 Bloomberg Terminal API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (≈$2,665/月,$31,980/年/席)</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="K20" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K21" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="K22" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="K23" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K24" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2732,14 +2732,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K25" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K25" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>无 SEC EDGAR 全文检索 API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2790,14 +2790,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K26" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K26" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·部分需付费</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>无 Quartr API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:部分付费 (Pro约$20/月起;API企业询价)</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="K27" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2906,14 +2906,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K28" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K28" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>无 Wind API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (含于Wind终端≈¥39,800/年)</t>
         </is>
       </c>
     </row>
@@ -2964,14 +2964,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K29" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K29" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·部分需付费</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>无 TipRanks API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;注册表:部分付费 (Premium≈$30/月;API询价)</t>
         </is>
       </c>
     </row>
@@ -3022,14 +3022,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K30" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K30" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>无 Visible Alpha API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;注册表:付费 (企业订阅,高,询价)</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="K31" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="K32" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3196,14 +3196,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K33" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K33" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>无 公开API provider 插件</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="K34" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3312,14 +3312,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K35" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K35" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>无 AlphaSense API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (≈$12k–20k/年/席)</t>
         </is>
       </c>
     </row>
